--- a/validacao/rotulos_guilherme.xlsx
+++ b/validacao/rotulos_guilherme.xlsx
@@ -442,9 +442,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -466,9 +464,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -518,9 +514,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -616,6 +610,21 @@
           <t>https://github.com/openclaw/openclaw</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Assistente IA auto-hospedavel; releases de pacote/binario usados pelo usuario final</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -631,6 +640,21 @@
           <t>https://github.com/tauri-apps/tauri</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Framework (crates/npm) publicado em releases versionadas</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -646,6 +670,21 @@
           <t>https://github.com/keras-team/keras</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Biblioteca multi-backend no PyPI</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -661,6 +700,21 @@
           <t>https://github.com/ClickHouse/ClickHouse</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Servidor de banco (binarios/packages oficiais por release)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -676,6 +730,21 @@
           <t>https://github.com/react/react-native</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Framework npm para apps nativos</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -691,6 +760,21 @@
           <t>https://github.com/pyenv/pyenv</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gerenciador de versoes do Python via terminal</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -706,6 +790,21 @@
           <t>https://github.com/nuxt/nuxt</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Framework Vue publicado no npm</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -721,6 +820,21 @@
           <t>https://github.com/facebookresearch/faiss</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Biblioteca C++/Python de busca por similaridade</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -736,6 +850,21 @@
           <t>https://github.com/BerriAI/litellm</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gateway/proxy LLM implantado; publicado em pypi/docker</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -751,6 +880,21 @@
           <t>https://github.com/microsoft/vscode</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Editor de codigo com releases mensais de binarios</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -766,6 +910,21 @@
           <t>https://github.com/remotion-dev/remotion</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Biblioteca React de video no npm</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -781,6 +940,21 @@
           <t>https://github.com/alibaba/open-code-review</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ferramenta de code review (npm) executada em terminal/CI</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -796,6 +970,21 @@
           <t>https://github.com/pocketbase/pocketbase</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Backend em arquivo unico; binario por release</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -811,6 +1000,21 @@
           <t>https://github.com/TanStack/query</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Conjunto de pacotes npm de estado/busca</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -826,6 +1030,21 @@
           <t>https://github.com/mrdoob/three.js</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Biblioteca JS 3D publicada no npm</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -841,6 +1060,21 @@
           <t>https://github.com/prometheus/prometheus</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Servidor de monitoramento; binarios/docker por release</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -856,6 +1090,21 @@
           <t>https://github.com/vllm-project/vllm</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motor de inferencia/servidor; pypi/docker</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -871,6 +1120,21 @@
           <t>https://github.com/payloadcms/payload</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CMS fullstack implantado pelo usuario; pacotes npm/docker</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -886,6 +1150,21 @@
           <t>https://github.com/jgm/pandoc</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Conversor de markup distribuido em binario</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -901,6 +1180,21 @@
           <t>https://github.com/mattpocock/skills</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>incerto</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Colecao de skills (conteudo) instalada via plugin; verificar se as releases acompanham o que o usuario recebe</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -916,6 +1210,21 @@
           <t>https://github.com/chakra-ui/chakra-ui</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sistema de componentes React no npm</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -931,6 +1240,21 @@
           <t>https://github.com/fastlane/fastlane</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Automacao de build/publicacao iOS/Android via terminal</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -946,6 +1270,21 @@
           <t>https://github.com/shadcn-ui/ui</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Conjunto de componentes publicado no npm</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -961,6 +1300,21 @@
           <t>https://github.com/sickn33/agentic-awesome-skills</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Catalogo + CLI (npx); releases versionadas acompanham a versao publicada e referenciada na docs</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -976,6 +1330,21 @@
           <t>https://github.com/ethereum/go-ethereum</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Cliente de no Ethereum; binarios oficiais</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -991,6 +1360,21 @@
           <t>https://github.com/Significant-Gravitas/AutoGPT</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Agente de IA com builds/binarios para o usuario</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1006,6 +1390,21 @@
           <t>https://github.com/upstash/context7</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Servidor MCP/plataforma; pacotes npm</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1021,6 +1420,21 @@
           <t>https://github.com/xtekky/gpt4free</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>App/pacote PyPI de acesso a LLMs</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1036,6 +1450,21 @@
           <t>https://github.com/langgenius/dify</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Plataforma auto-hospedavel; imagens docker</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1051,6 +1480,21 @@
           <t>https://github.com/roboflow/supervision</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Biblioteca Python de visao computacional no PyPI</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1066,6 +1510,21 @@
           <t>https://github.com/Fission-AI/OpenSpec</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CLI de desenvolvimento orientado a spec; npm</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1081,6 +1540,21 @@
           <t>https://github.com/mastodon/mastodon</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rede social auto-hospedavel; imagens docker</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1096,6 +1570,21 @@
           <t>https://github.com/Mintplex-Labs/anything-llm</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>App local-first (docker/desktop) para o usuario</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1111,6 +1600,21 @@
           <t>https://github.com/Imbad0202/academic-research-skills</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Suite de skills (conteudo) instalada como plugin versionado; README anuncia a versao atual das releases</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1126,6 +1630,21 @@
           <t>https://github.com/pingcap/tidb</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Banco distribuido; binarios/charts</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1141,6 +1660,21 @@
           <t>https://github.com/ggml-org/llama.cpp</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Motor de inferencia com CLI/servidor; binarios e nightlies</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1156,6 +1690,21 @@
           <t>https://github.com/ChrisTitusTech/winutil</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Utilitario de Windows com interface para o usuario</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1171,6 +1720,21 @@
           <t>https://github.com/crewAIInc/crewAI</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Framework Python de orquestracao de agentes no PyPI</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1186,6 +1750,21 @@
           <t>https://github.com/ToolJet/ToolJet</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Plataforma auto-hospedavel de ferramentas internas; docker</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1201,6 +1780,21 @@
           <t>https://github.com/browser-use/browser-use</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Biblioteca Python de automacao de navegador no PyPI</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1216,6 +1810,21 @@
           <t>https://github.com/danielmiessler/Fabric</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Framework de prompts executado via CLI</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1231,6 +1840,21 @@
           <t>https://github.com/career-ops-hq/career-ops</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Agente de busca de emprego que roda no CLI</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1246,6 +1870,21 @@
           <t>https://github.com/vercel-labs/agent-browser</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>CLI nativa de automacao de navegador; npm</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1261,6 +1900,21 @@
           <t>https://github.com/ant-design/ant-design</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Biblioteca UI React no npm</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1276,6 +1930,21 @@
           <t>https://github.com/ccxt/ccxt</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Biblioteca unificada de exchanges no npm/PyPI</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1291,6 +1960,21 @@
           <t>https://github.com/apple/container</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CLI para containers em VMs leves no Mac; binarios</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1306,6 +1990,21 @@
           <t>https://github.com/reactive-resume/reactive-resume</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Construtor de curriculos auto-hospedavel; docker</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1321,6 +2020,21 @@
           <t>https://github.com/rails/rails</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Framework web publicado como gem</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1336,6 +2050,21 @@
           <t>https://github.com/fastapi/fastapi</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Framework web no PyPI</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1351,6 +2080,21 @@
           <t>https://github.com/react-hook-form/react-hook-form</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Hook React de formularios no npm</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1366,6 +2110,21 @@
           <t>https://github.com/moeru-ai/airi</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Companheiro de IA auto-hospedavel; builds web/desktop</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1381,6 +2140,21 @@
           <t>https://github.com/janhq/jan</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>App desktop offline; instaladores por release</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1396,6 +2170,21 @@
           <t>https://github.com/rtk-ai/rtk</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Proxy CLI em binario unico Rust</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1411,6 +2200,21 @@
           <t>https://github.com/calcom/cal.diy</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Infraestrutura de agendamento auto-hospedavel</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1426,6 +2230,21 @@
           <t>https://github.com/zed-industries/zed</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Editor de codigo com instaladores oficiais</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1441,6 +2260,21 @@
           <t>https://github.com/typst/typst</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Sistema de composicao tipografica com CLI; binarios/crates</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1456,6 +2290,21 @@
           <t>https://github.com/denoland/deno</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Runtime de JavaScript/TypeScript instalado pelo usuario</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1471,6 +2320,21 @@
           <t>https://github.com/dani-garcia/vaultwarden</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Servidor Bitwarden compativel; binarios/docker</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1486,6 +2350,21 @@
           <t>https://github.com/nexu-io/open-design</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Workspace de design colaborativo local-first</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1499,6 +2378,21 @@
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>https://github.com/JuliaLang/julia</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Linguagem/runtime instalado pelo usuario; binarios por release</t>
         </is>
       </c>
     </row>
@@ -1674,6 +2568,16 @@
           <t>https://github.com/openclaw/openclaw/compare/v1.2.0...v1.2.1</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>notes abrem com feat de heartbeat; 6 de 8 commits sao docs/chore e apenas 1 fix de media</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1707,6 +2611,16 @@
           <t>https://github.com/openclaw/openclaw/compare/v2026.1.11...v2026.1.11-1</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>hotfix cujo unico item de notes e correcao do installer (patches/ no pacote npm)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1740,6 +2654,16 @@
           <t>https://github.com/openclaw/openclaw/compare/v2026.2.21...v2026.2.22</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>notes apenas novidades (provedor Mistral, canal Synology, auto-updater); mistura de commits</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1773,6 +2697,16 @@
           <t>https://github.com/openclaw/openclaw/compare/v2026.2.23...v2026.2.24</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>74 itens em Fixes contra 5 em Changes; 40 de 61 commits listados sao correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1806,6 +2740,16 @@
           <t>https://github.com/openclaw/openclaw/compare/v2026.5.7...v2026.5.12</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>notes com 372 itens em Fixes contra 76 em Changes; correcoes dominam por larga margem</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1839,6 +2783,16 @@
           <t>https://github.com/tauri-apps/tauri/compare/tauri-build-v2.5.0...tauri-v2.9.0</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>minor 2.9.0: New Features(4) e Dependencies(5) superam Bug Fixes(2); commits indisponiveis</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1872,6 +2826,16 @@
           <t>https://github.com/tauri-apps/tauri/compare/@tauri-apps/api-v2.11.0...tauri-utils-v2.9.0</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>notes apenas New Features e Dependencies, sem secao de correcoes; commits indisponiveis</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1905,6 +2869,16 @@
           <t>https://github.com/tauri-apps/tauri/compare/tauri-v2.11.2...@tauri-apps/cli-v2.11.2</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>unico conteudo e bump de dependencia tauri-cli 2.11.2; atualizacao de rotina</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1938,6 +2912,16 @@
           <t>https://github.com/tauri-apps/tauri/compare/tauri-codegen-v3.0.0-alpha.0...tauri-macros-v3.0.0-alpha.0</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>alpha com New Features, Performance e Breaking Changes; nenhuma secao de correcao</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1971,6 +2955,16 @@
           <t>https://github.com/tauri-apps/tauri/compare/tauri-v3.0.0-alpha.4...tauri-runtime-wry-v3.0.0-alpha.4</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>notes apenas Upgrade de dependencias e Breaking Changes; rotina de release alpha</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2004,6 +2998,16 @@
           <t>https://github.com/keras-team/keras/compare/v3.11.3...v3.12.0</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>destaques sao novas APIs (destilacao de modelos e quantizacao GPTQ); sem correcao</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2037,6 +3041,16 @@
           <t>https://github.com/keras-team/keras/compare/v3.12.1...v3.14.0</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Highlights sao novidades (Orbax, AWQ, BatchRenorm, ScheduleFreeAdamW) e paridade OpenVINO</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2070,6 +3084,16 @@
           <t>https://github.com/keras-team/keras/compare/v3.14.1...v3.15.0</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5 de 6 destaques sao funcionalidades (export_torch, MultiOptimizer); hardening e 1 so</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2103,6 +3127,16 @@
           <t>https://github.com/keras-team/keras/compare/v3.15.0...v3.12.3</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>patch de seguranca explicito: hardening HDF5 e arquivos .keras contra traversal e bombs</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2136,6 +3170,16 @@
           <t>https://github.com/keras-team/keras/compare/v3.12.3...v3.15.1</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>patch com 4 Security Fixes e 2 Bug Fixes; apenas 1 item e compatibilidade Python 3.14</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2169,6 +3213,16 @@
           <t>https://github.com/ClickHouse/ClickHouse/compare/v25.8.11.66-lts...v25.9.5.21-stable</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>stable mensal sem notes; commits misturados: ~24 fixes de 60, resto features/docs/CI</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2202,6 +3256,16 @@
           <t>https://github.com/ClickHouse/ClickHouse/compare/v25.10.3.100-stable...v25.8.12.129-lts</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>LTS de patch quase integralmente backports de fixes (crash, vazamento, corrupcao)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2235,6 +3299,16 @@
           <t>https://github.com/ClickHouse/ClickHouse/compare/v26.2.6.27-stable...v26.2.7.17-stable</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>34 commits todos backports de correcoes, incl. vazamento cross-user em system table</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2268,6 +3342,16 @@
           <t>https://github.com/ClickHouse/ClickHouse/compare/v26.3.10.60-lts...v26.1.12.23-stable</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>backports de 26.1 dominados por fixes (segfault, heap-use-after-free, crash em merge)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2301,6 +3385,16 @@
           <t>https://github.com/ClickHouse/ClickHouse/compare/v26.6.2.160-stable...v26.7.3.19-stable</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>stable mensal sem notes; commits misturados com docs/CI/features e ~15 fixes em 60</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2334,6 +3428,16 @@
           <t>https://github.com/react/react-native/compare/v0.81.4...v0.82.0</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>minor 0.82.0 com feats (DOM APIs estaveis, monitor de perf) e refactors; mistura</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2367,6 +3471,16 @@
           <t>https://github.com/react/react-native/compare/v0.83.2...v0.81.6</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>patch da branch 0.81; commits substanciais com 18 fixes contra 8 feats/chore</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2400,6 +3514,16 @@
           <t>https://github.com/react/react-native/compare/v0.81.6...v0.84.0</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>minor 0.84.0; commits misturados de frame timings, VirtualView e refators, sem foco</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2433,6 +3557,16 @@
           <t>https://github.com/react/react-native/compare/v0.83.9...v0.85.3</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>patch de build: notas com 4 itens em Fixed contra 1 em Changed; correcoes dominam</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2466,6 +3600,16 @@
           <t>https://github.com/react/react-native/compare/v0.86.2...v0.87.0</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>minor 0.87.0; feats (CDP, estilo backgroundImage) e refators misturados com fixes</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2499,6 +3643,16 @@
           <t>https://github.com/pyenv/pyenv/compare/v2.6.21...v2.6.22</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>unico conteudo e adicao do CPython 3.13.12; atualizacao de rotina</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2532,6 +3686,16 @@
           <t>https://github.com/pyenv/pyenv/compare/v2.6.23...v2.6.24</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>mistura de CI, adicao de versoes do Python e melhoria de rehash; correcao nao principal</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2565,6 +3729,16 @@
           <t>https://github.com/pyenv/pyenv/compare/v2.6.29...v2.6.30</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>unico conteudo e adicao do CPython 3.16-dev; atualizacao de rotina</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2598,6 +3772,16 @@
           <t>https://github.com/pyenv/pyenv/compare/v2.6.32...v2.7.1</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>mistura de features (init --install), novas versoes de Python e 1 fix de sintaxe</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2631,6 +3815,16 @@
           <t>https://github.com/pyenv/pyenv/compare/v2.7.2...v2.7.3</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>CI add_version e adicao do CPython 3.15.0b3; nenhum foco em correcao</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2664,6 +3858,16 @@
           <t>https://github.com/nuxt/nuxt/compare/v4.2.2...v3.21.0</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>minor release com novidades (route rule layouts, cache) e backports; mistura</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2697,6 +3901,16 @@
           <t>https://github.com/nuxt/nuxt/compare/v4.3.1...v4.4.0</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>minor 4.4.0 com createUseFetch/createUseAsyncData e vue-router v5; features dominam</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2730,6 +3944,16 @@
           <t>https://github.com/nuxt/nuxt/compare/v3.21.5...v4.4.5</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>patch: 18 itens em Fixes contra 1 Performance, 1 Doc e 6 Chore; sem secao de features</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2763,6 +3987,16 @@
           <t>https://github.com/nuxt/nuxt/compare/v3.21.8...v4.4.8</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>hotfix explicito para dev server no MacOS; secao Fixes domina o changelog</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2796,6 +4030,16 @@
           <t>https://github.com/nuxt/nuxt/compare/v3.21.10...v4.5.2</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>patch com ~25 Fixes contra 4 Performance, 2 Refactors e 8 Docs; sem features</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2829,6 +4073,16 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.12.0...v1.13.0</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>lista Added domina as notas (PanoramaStats, RaBitQ, IVFFlat); release de features</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2862,6 +4116,16 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.13.0...v1.13.1</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>notas divididas: 5 Added, 6 Changed e apenas 4 Fixed; correcao nao principal</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2895,6 +4159,16 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.14.1...v1.14.2</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Highlights sao funcionalidades (SuperKMeans, Metal, pip install); hardening e 1 so</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2928,6 +4202,16 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.14.3...v1.15.0</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>secao Added do changelog domina com novos indexes e backends; release de funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2961,6 +4245,16 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.15.0...v1.15.1</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>notes remetem ao changelog; ~28 de 60 commits sao fixes (OOB, data race, overflow)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2994,6 +4288,16 @@
           <t>https://github.com/BerriAI/litellm/compare/v1.79.dev.1...v1.79.3.dev2</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>conteudo e hook Zscaler AI Guard e bump de docker no CI; sem correcao</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3027,6 +4331,16 @@
           <t>https://github.com/BerriAI/litellm/compare/v1.80.5.dev32...v1.80.6-nightly</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>nightly com feats (uso de organizacao, WatsonX, RAG API); fixes sao minoria</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3060,6 +4374,16 @@
           <t>https://github.com/BerriAI/litellm/compare/v1.81.14.dev.1...v1.82.3.dev.3</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>notes dominadas por features de UI; os 5 commits 'fix' sao ajustes de revisao de PR</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3093,6 +4417,16 @@
           <t>https://github.com/BerriAI/litellm/compare/v1.96.2...v1.97.0</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>143 de 258 itens de What's Changed sao fix contra 33 feat; correcoes dominam</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3126,6 +4460,16 @@
           <t>https://github.com/BerriAI/litellm/compare/v1.100.4...v1.101.3</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>sem changelog nas notes; commits substanciais com ~20 fixes contra ~16 nao-fix</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3159,6 +4503,16 @@
           <t>https://github.com/microsoft/vscode/compare/1.104.2...1.104.3</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>release de recuperacao que endereca issues fechadas do milestone Recovery 3</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3192,6 +4546,16 @@
           <t>https://github.com/microsoft/vscode/compare/1.106.1...1.106.2</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>recovery release; commits citam fixes de issues (#277023, #277352) e correcoes de UI</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3225,6 +4589,16 @@
           <t>https://github.com/microsoft/vscode/compare/1.126.0...1.127.0</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>monthly release com notes genericas e feats (agents, voz, sandboxing); mistura</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3258,6 +4632,16 @@
           <t>https://github.com/microsoft/vscode/compare/1.136.1...1.136.2</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>patch de seguranca: fixes MSRC, path traversal de webview/MCP e bypass de Restricted Mode</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3291,6 +4675,16 @@
           <t>https://github.com/microsoft/vscode/compare/1.139.0...1.139.1</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>patch pequeno cujo unico cambio funcional e correcao cherry-pick de managed settings</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3324,6 +4718,16 @@
           <t>https://github.com/remotion-dev/remotion/compare/v4.0.388...v4.0.390</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2 fixes no topo das notes, mas 27 de 37 commits constroem a feature text node handling</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3357,6 +4761,16 @@
           <t>https://github.com/remotion-dev/remotion/compare/v4.0.390...v4.0.391</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>notes listam ~10 correcoes vs 1 bloco de docs; maioria dos commits tambem e correcao</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3390,6 +4804,16 @@
           <t>https://github.com/remotion-dev/remotion/compare/v4.0.482...v4.0.483</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>mistura: 8 features de studio/effects vs ~6 fixes alem de 7 itens de docs</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3423,6 +4847,16 @@
           <t>https://github.com/remotion-dev/remotion/compare/v4.0.501...v4.0.502</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>funcionalidades dominam (studio protocol, rspack, stills, asset picker); fixes sao minoria</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3456,6 +4890,16 @@
           <t>https://github.com/remotion-dev/remotion/compare/v4.0.506...v4.0.507</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>grande maioria de features/melhorias de studio e convert; fixes sao minoria dos commits</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3489,6 +4933,16 @@
           <t>https://github.com/alibaba/open-code-review/compare/v1.1.10...v1.1.11</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>unico objetivo e feat(build) de suporte a Windows; o fix e apenas follow-up do review</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3522,6 +4976,16 @@
           <t>https://github.com/alibaba/open-code-review/compare/v1.3.3...v1.3.4</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>commit unico e ajuste de CI (flag de provenance); manutencao de rotina sem defeito no produto</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3555,6 +5019,16 @@
           <t>https://github.com/alibaba/open-code-review/compare/v1.6.3...v1.6.4</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>conteudo apenas de docs (GOVERNANCE, ROADMAP) e CI (govulncheck, dependabot); nenhuma correcao</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3588,6 +5062,16 @@
           <t>https://github.com/alibaba/open-code-review/compare/v1.9.5...v1.9.6</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>7 features vs 6 fixes; secao Features lidera notes e commits</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3621,6 +5105,16 @@
           <t>https://github.com/alibaba/open-code-review/compare/v1.12.4...v1.12.5</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10 features vs 6 fixes; release dominada por novas funcionalidades de UI</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3654,6 +5148,16 @@
           <t>https://github.com/pocketbase/pocketbase/compare/v0.30.3...v0.30.4</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>unico objetivo e corrigir regressao de CSS do campo json introduzida em v0.30.3</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3687,6 +5191,16 @@
           <t>https://github.com/pocketbase/pocketbase/compare/v0.34.0...v0.22.37</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>backport de rotina: deps, changelog e fixes misturados; Go action bump por security fix</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3720,6 +5234,16 @@
           <t>https://github.com/pocketbase/pocketbase/compare/v0.36.0...v0.36.1</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>notes lideram com revert de otimizacao que degradou index; dep update e typos sao secundarios</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3753,6 +5277,16 @@
           <t>https://github.com/pocketbase/pocketbase/compare/v0.36.9...v0.37.0</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>release de maior: nova UI reescrita do zero; commits sao da feature, nao fixes</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3786,6 +5320,16 @@
           <t>https://github.com/pocketbase/pocketbase/compare/v0.39.3...v0.39.4</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>7 de 10 commits sao fixes e notes abrem com correcao do #7734; ha 1 feature</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3819,6 +5363,16 @@
           <t>https://github.com/TanStack/query/compare/@tanstack/react-query-next-experimental@5.100.11...@tanstack/react-query-persist-client@5.100.11</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>notes apenas atualizam dependencias; sem mudanca funcional ou correcao</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3852,6 +5406,16 @@
           <t>https://github.com/TanStack/query/compare/@tanstack/solid-query-persist-client@5.100.13...@tanstack/eslint-plugin-query@5.100.13</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>notes vazias e commits indisponiveis; sem evidencia de correcao, release de rotina</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3885,6 +5449,16 @@
           <t>https://github.com/TanStack/query/compare/@tanstack/react-query-devtools@5.100.14...@tanstack/lit-query@0.2.6</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>notes apenas atualizam @tanstack/query-core; bump de dependencia de rotina</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3918,6 +5492,16 @@
           <t>https://github.com/TanStack/query/compare/@tanstack/query-sync-storage-persister@5.101.0...@tanstack/angular-query-experimental@5.101.0</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>notes apenas atualizam query-core; bump de dependencia de rotina sem correcao</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3951,6 +5535,16 @@
           <t>https://github.com/TanStack/query/compare/@tanstack/solid-query@5.103.0...@tanstack/query-devtools@5.103.0</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>mudanca principal corrige resolucao de dependencias em package managers estritos; resto e bump</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3984,6 +5578,16 @@
           <t>https://github.com/mrdoob/three.js/compare/r180...r181</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>release trimestral com centenas de commits: features WebGPU/TSL/Inspector superam fixes</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4017,6 +5621,16 @@
           <t>https://github.com/mrdoob/three.js/compare/r181...r182</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>release trimestral mistura novas features (Inspector, SVGRenderer, TSL) com fixes</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4050,6 +5664,16 @@
           <t>https://github.com/mrdoob/three.js/compare/r182...r183</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>milestone dominada por features (Editor, USDLoader, Object3D pivot) e refactors</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4083,6 +5707,16 @@
           <t>https://github.com/mrdoob/three.js/compare/r184...r185</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>milestone mistura features e fixes; centenas de commits e funcionalidades dominam</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4116,6 +5750,16 @@
           <t>https://github.com/mrdoob/three.js/compare/r185...r186</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>milestone traz gaussian splat, transpiler e novas features; fixes sao minoria</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4149,6 +5793,16 @@
           <t>https://github.com/prometheus/prometheus/compare/v3.6.0...v3.7.0</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>release menor agendada com CHANGE, FEATURE e ENHANCEMENT; correcoes nao sao o foco</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4182,6 +5836,16 @@
           <t>https://github.com/prometheus/prometheus/compare/v3.9.1...v3.5.1</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>sem mudancas de codigo; apenas bumps de dependencias (docker, Go) de rotina</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4215,6 +5879,16 @@
           <t>https://github.com/prometheus/prometheus/compare/v3.11.0...v3.11.1</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>unico item do changelog e BUGFIX de falha de inicializacao de tracing OTLP HTTP</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4248,6 +5922,16 @@
           <t>https://github.com/prometheus/prometheus/compare/v3.11.3...v3.12.0</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>release menor agendada: 13 features, ~22 bugfixes e 2 de seguranca; mistura sem foco unico</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4281,6 +5965,16 @@
           <t>https://github.com/prometheus/prometheus/compare/v3.13.3...v3.15.0</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>release menor v3.15.0 com novos recursos (UDS, OM2.0, runtime.log_level) e melhorias</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4314,6 +6008,16 @@
           <t>https://github.com/vllm-project/vllm/compare/v0.15.0...v0.15.1</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>patch de seguranca com 2 CVEs; 14 de 22 commits sao fixes e apenas 1 modelo novo</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4347,6 +6051,16 @@
           <t>https://github.com/vllm-project/vllm/compare/v0.19.0...v0.19.1</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>13 de 19 commits sao fixes (Gemma4/CI); upgrade do transformers e item secundario</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4380,6 +6094,16 @@
           <t>https://github.com/vllm-project/vllm/compare/v0.20.0...v0.20.1</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>16 de 29 commits sao fixes e notes destacam estabilizacao do DeepSeek V4</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4413,6 +6137,16 @@
           <t>https://github.com/vllm-project/vllm/compare/v0.24.0...v0.25.0</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>release menor com 558 commits, novos modelos e features; correcoes sao minoria</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4446,6 +6180,16 @@
           <t>https://github.com/vllm-project/vllm/compare/v0.27.1...v0.28.0</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>release menor com 584 commits de features (Kimi-K3, DSV4, MRV2); foco em novidades</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4479,6 +6223,16 @@
           <t>https://github.com/payloadcms/payload/compare/v3.68.0...v3.68.1</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>unico commit evita sugerir Next.js vulneravel; patch cujo conteudo todo e correcao</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4512,6 +6266,16 @@
           <t>https://github.com/payloadcms/payload/compare/v3.68.4...v3.68.5</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1 fix (route matching) lidera os notes; o outro commit e refactor interno de apoio</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4545,6 +6309,16 @@
           <t>https://github.com/payloadcms/payload/compare/v3.78.0...v3.79.0</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>release menor com 3 features destacadas e prosa longa; fixes sao rotineiros da milestone</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4578,6 +6352,16 @@
           <t>https://github.com/payloadcms/payload/compare/v3.84.1...v3.85.0</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>11 de 19 commits sao fixes e notes trazem 8 bugfixes (incl. GHSA) vs 1 feature</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4611,6 +6395,16 @@
           <t>https://github.com/payloadcms/payload/compare/v3.87.1...v3.88.0</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2 fixes de seguranca (backtracking e clipboard) lideram; refactor e bump sao apoio</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4644,6 +6438,16 @@
           <t>https://github.com/jgm/pandoc/compare/3.8.1...3.8.2</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>anuncio lidera com correcao de regressao do template typst; fixes lideram entre funcionais</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4677,6 +6481,16 @@
           <t>https://github.com/jgm/pandoc/compare/3.8.2.1...3.8.3</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>anuncio comeca destacando 4 formatos novos (asciidoc, pptx, xlsx, bbcode); fixes secundarios</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4710,6 +6524,16 @@
           <t>https://github.com/jgm/pandoc/compare/3.9.0.1...3.9.0.2</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>anuncio e changelog dizem que a release apenas corrige regressao do template typst</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4743,6 +6567,16 @@
           <t>https://github.com/jgm/pandoc/compare/3.10.2...3.11</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>release menor com opcoes novas (--math-method, --completion) e RTL; fixes sao menores</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4776,6 +6610,16 @@
           <t>https://github.com/jgm/pandoc/compare/3.11...3.12</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>foco declarado e performance; otimizacoes e melhorias dominam, nao correcao de defeitos</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4809,6 +6653,16 @@
           <t>https://github.com/mattpocock/skills/compare/mattpocock-skills@1.0.0...v1.0.0</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>notes trazem novas skills e mudancas breaking; commit listado e apenas CI de release</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4842,6 +6696,16 @@
           <t>https://github.com/mattpocock/skills/compare/v1.0.0...v1.0.1</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>commits sao feat/chore de conteudo da skill teach; nenhuma correcao</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4875,6 +6739,16 @@
           <t>https://github.com/mattpocock/skills/compare/v1.0.1...v1.1.0</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Minor Changes com novos skills/promocao de code-review; maioria e feat e docs</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4908,6 +6782,16 @@
           <t>https://github.com/mattpocock/skills/compare/v1.2.0...v1.2.2</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>unico item funcional restaura invocacao da skill no Codex (regressao); resto e docs/chore</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4941,6 +6825,16 @@
           <t>https://github.com/mattpocock/skills/compare/v1.2.2...v1.2.3</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>4 de 6 commits funcionais sao fix (redacao de segredos e instrucoes cross-harness)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4974,6 +6868,16 @@
           <t>https://github.com/chakra-ui/chakra-ui/compare/@chakra-ui/react@3.27.0...@chakra-ui/panda-preset@3.27.1</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>notes vazias; 36 commits mixos: docs/chore/refactor e bumps de deps dominam, correcoes nao sao o principal</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -5007,6 +6911,16 @@
           <t>https://github.com/chakra-ui/chakra-ui/compare/@chakra-ui/charts@3.28.0...@chakra-ui/cli@3.28.0</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>sem release notes e commits indisponiveis; tag minor 3.28.0 sem qualquer evidencia de correcao</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5040,6 +6954,16 @@
           <t>https://github.com/chakra-ui/chakra-ui/compare/@chakra-ui/charts@3.29.0...@chakra-ui/react@3.30.0</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>minor change destaca novo componente Splitter; fixes sao minoritarios nas notes e nos 36 commits</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5073,6 +6997,16 @@
           <t>https://github.com/chakra-ui/chakra-ui/compare/@chakra-ui/panda-preset@3.31.0...@chakra-ui/charts@3.31.0</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>release notes vazias e commits indisponiveis; tag minor 3.31.0 sem evidencia de correcao</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5106,6 +7040,16 @@
           <t>https://github.com/chakra-ui/chakra-ui/compare/@chakra-ui/codemod@3.34.0...@chakra-ui/react@3.34.0</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>minor change principal e novo DatePicker; patches de correcao sao secundarios; commits indisponiveis</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5139,6 +7083,16 @@
           <t>https://github.com/fastlane/fastlane/compare/2.228.0...2.229.0</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>mistura de manutencao de CI e suporte Ruby 3.4 (feature); correcoes de CI nao sao o objetivo principal</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5172,6 +7126,16 @@
           <t>https://github.com/fastlane/fastlane/compare/2.229.0...2.229.1</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>patch pos-2.229.0 so com correcoes do pipeline de release e build (4 itens), sem funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5205,6 +7169,16 @@
           <t>https://github.com/fastlane/fastlane/compare/2.231.1...2.232.0</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>mistura: features (API de uploads, certificados, opcoes xcodebuild) e fixes de CI/appium; correcao nao principal</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5238,6 +7212,16 @@
           <t>https://github.com/fastlane/fastlane/compare/2.232.2...2.233.0</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>23 itens com maioria de features (upload de previews, STS, tokens, flags); fixes sao minoritarios</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5271,6 +7255,16 @@
           <t>https://github.com/fastlane/fastlane/compare/2.234.0...2.235.0</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>mistura equilibrada: ~8 fixes vs ~8 features (App Clips, endpoint supply, Ruby 3.0 min); correcao nao domina</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5304,6 +7298,16 @@
           <t>https://github.com/shadcn-ui/ui/compare/shadcn@3.5.0...shadcn@3.5.1</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>notes trazem 3 correcoes, mas 108 commits sao majoritariamente feats de registro e chores do monorepo</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5337,6 +7341,16 @@
           <t>https://github.com/shadcn-ui/ui/compare/shadcn@3.6.2...shadcn@3.6.3</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>notes empatadas entre fix e feat (MCP opencode); commits majoritariamente chores/registry do diretorio</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5370,6 +7384,16 @@
           <t>https://github.com/shadcn-ui/ui/compare/shadcn@3.8.4...shadcn@3.8.5</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>unico item das notes e fix, mas 69 commits dominados por feats de registry e chores; correcao nao principal</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5403,6 +7427,16 @@
           <t>https://github.com/shadcn-ui/ui/compare/shadcn@4.7.0...shadcn@4.8.0</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>minor change com 2 funcs novas (validate command, include); 29 commits com maioria de feats de registro</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5436,6 +7470,16 @@
           <t>https://github.com/shadcn-ui/ui/compare/shadcn@4.12.0...@shadcn/react@0.2.0</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>initial release do novo pacote @shadcn/react; commits trazem funcs e fixes misturados</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5469,6 +7513,16 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v2.4.0...v2.5.0</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>release adiciona nova skill remotion-best-practices; unico commit e feat</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5502,6 +7556,16 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v8.3.0...v8.4.0</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>notes autodenominam corte de discovery/melhorias/curadoria de metadata; fixes de web-app sao secundarios</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5535,6 +7599,16 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v10.9.0...v10.10.0</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>duas novas skills (production-audit, context-pruning) lideram a release; apenas 1 fix de link</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5568,6 +7642,16 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v13.0.0...v13.1.0</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>3 novas skills de comunidade + credits; commits majoritariamente feats e sync de registro</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5601,6 +7685,16 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v18.9.0...v18.10.0</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>adiciona 124 skills e novo catalogo; 10 advisories fechados mas feats dominam (54 commits)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5634,6 +7728,16 @@
           <t>https://github.com/ethereum/go-ethereum/compare/v1.16.4...v1.16.5</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>maintenance release emitida 'mostly' para adicionar conversion path de blob proofs (feature)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5667,6 +7771,16 @@
           <t>https://github.com/ethereum/go-ethereum/compare/v1.16.9...v1.17.0</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>autodescrita como feature release de 3 meses; inclui CVEs mas v1.16.9 cobre so as correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -5700,6 +7814,16 @@
           <t>https://github.com/ethereum/go-ethereum/compare/v1.17.2...v1.17.3</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>maintenance release centrada no fork Amsterdam e protocolos eth/70, snap/2; features dominam</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5733,6 +7857,16 @@
           <t>https://github.com/ethereum/go-ethereum/compare/v1.17.3...v1.17.4</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>mistura equilibrada: fixes ~metade dos commits, mas fork Amsterdam e novos RPCs vem primeiro nas notes</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -5766,6 +7900,16 @@
           <t>https://github.com/ethereum/go-ethereum/compare/v1.17.5...v1.17.6</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>foco declarado em melhorias de performance e agendamento do fork; fixes nao sao o principal</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -5799,6 +7943,16 @@
           <t>https://github.com/Significant-Gravitas/AutoGPT/compare/autogpt-platform-beta-v0.6.54...autogpt-platform-beta-v0.6.55</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>notes lideram com 8 features novas; 143 commits com feats de chat panel e billing dominando</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -5832,6 +7986,16 @@
           <t>https://github.com/Significant-Gravitas/AutoGPT/compare/autogpt-platform-beta-v0.6.56...autogpt-platform-beta-v0.6.57</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>lista longa de novas features (billing, dashboards, modelos); fixes sao secundarios</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -5865,6 +8029,16 @@
           <t>https://github.com/Significant-Gravitas/AutoGPT/compare/autogpt-platform-beta-v0.6.57...autogpt-platform-beta-v0.6.58</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>New Features domina as notes (settings v2, billing, notificacoes); mistura com fixes minoritarios</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -5898,6 +8072,16 @@
           <t>https://github.com/Significant-Gravitas/AutoGPT/compare/autogpt-platform-beta-v0.6.70...autogpt-platform-beta-v0.7.0</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>release minor 0.7.0: Better Auth, marketplace, catalogo de modelos; 7 feats vs 5 fixes</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -5931,6 +8115,16 @@
           <t>https://github.com/Significant-Gravitas/AutoGPT/compare/autogpt-platform-beta-v0.7.2...autogpt-platform-beta-v0.7.3</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>7 features novas e 4 melhorias de UI contra ~6 fixes; correcao nao e o principal</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -5964,6 +8158,16 @@
           <t>https://github.com/upstash/context7/compare/v1.0.24...v1.0.25</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>unico commit e chore de atualizacao de schema; notes sem mudancas de correcao</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -5997,6 +8201,16 @@
           <t>https://github.com/upstash/context7/compare/ctx7@0.3.8...@upstash/context7-mcp@2.1.6</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>commits indisponiveis; notes trazem apenas ajustes de texto e metadata do servidor</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -6030,6 +8244,16 @@
           <t>https://github.com/upstash/context7/compare/ctx7@0.3.9...@upstash/context7-mcp@2.1.7</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>notes trazem feat (--version) e melhoria de prompt; 9 commits com feats/docs dominando</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -6063,6 +8287,16 @@
           <t>https://github.com/upstash/context7/compare/ctx7@0.3.12...@upstash/context7-mcp@2.1.8</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>unico item das notes corrige carga de CAs com NODE_EXTRA_CA_CERTS e adiciona teste de regressao</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -6096,6 +8330,16 @@
           <t>https://github.com/upstash/context7/compare/ctx7@0.4.5...ctx7@0.5.0</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>nota unica introduz OAuth device flow (RFC 8628), funcionalidade nova</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -6129,6 +8373,16 @@
           <t>https://github.com/xtekky/gpt4free/compare/v6.5.5...v6.5.6</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>3 commits: 2 feats (ferramentas MCP/CORS) e 1 fix; funcionalidades sao o principal</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -6162,6 +8416,16 @@
           <t>https://github.com/xtekky/gpt4free/compare/v7.1.4...v7.1.5</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>4 commits de atualizacao de provedores (Copilot/Gemini/Antigravity) sem correcao declarada</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -6195,6 +8459,16 @@
           <t>https://github.com/xtekky/gpt4free/compare/v7.4.6...v7.4.7</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>unico commit do release e um Fix (parameter assignment); notes nao trazem funcionalidade</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -6228,6 +8502,16 @@
           <t>https://github.com/xtekky/gpt4free/compare/v7.9.2...v7.9.3</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>3 commits apenas atualizam requirements.txt e setup.py; rotina de dependencias</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -6261,6 +8545,16 @@
           <t>https://github.com/xtekky/gpt4free/compare/v8.1.8...v8.2.0</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>3 commits vagos (headers, scripts, resolve path); apenas 1 fix e minor 8.2.0 sem notas de correcao</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -6294,6 +8588,16 @@
           <t>https://github.com/langgenius/dify/compare/1.9.1...1.9.2</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>notes lideram com highlights de features e melhorias; 250 commits mistos; fixes em secao propria</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -6327,6 +8631,16 @@
           <t>https://github.com/langgenius/dify/compare/1.11.3...1.11.4</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>patch de seguranca (CVE de DoS em Node) e 3 fixes; 4 de 5 commits sao correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -6360,6 +8674,16 @@
           <t>https://github.com/langgenius/dify/compare/1.11.4...1.12.0</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>minor release com nova Summary Index; 249 commits mistos com feats e refactors dominando</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -6393,6 +8717,16 @@
           <t>https://github.com/langgenius/dify/compare/1.13.3...1.14.0</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>novas features de colaboracao e HITL lideram; 250 commits com refactors e feats majoritarios</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -6426,6 +8760,16 @@
           <t>https://github.com/langgenius/dify/compare/1.14.1...1.14.2</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>patch de seguranca e confiabilidade: tenant scoping, tracing, RAG; ~30 fixes em 60 commits</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -6459,6 +8803,16 @@
           <t>https://github.com/roboflow/supervision/compare/0.26.1...0.27.0</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>secao Added lidera com novas APIs (edit_distance, keypoints, spline); minor de funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -6492,6 +8846,16 @@
           <t>https://github.com/roboflow/supervision/compare/0.29.0.post0...0.29.1</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>7 correcoes vs 1 feature nova nas notes; 9 de 11 commits substantivos sao fixes</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -6525,6 +8889,16 @@
           <t>https://github.com/roboflow/supervision/compare/0.30.1...0.30.2</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>notes autodenominam 'numeric-correctness fixes'; 4 fixes de deteccao, nenhuma API nova</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -6558,6 +8932,16 @@
           <t>https://github.com/roboflow/supervision/compare/0.30.2...0.30.3</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>bug-fix release de crashes e correcoes; 14 de 22 commits sao fixes</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -6591,6 +8975,16 @@
           <t>https://github.com/roboflow/supervision/compare/0.30.4...0.30.5</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>patch fecha 11 bugs de correcao e crash; 11 de 17 commits sao fixes</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -6624,6 +9018,16 @@
           <t>https://github.com/Fission-AI/OpenSpec/compare/v1.0.2...v1.1.0</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>release de estabilidade; secao Fixed (4 itens) domina Improved (2); texto declara foco em fixes</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -6657,6 +9061,16 @@
           <t>https://github.com/Fission-AI/OpenSpec/compare/v1.1.0...v1.1.1</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>patch rapido cujo unico proposito e corrigir referencias de comandos OpenCode; 3 commits fix</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -6690,6 +9104,16 @@
           <t>https://github.com/Fission-AI/OpenSpec/compare/v1.7.0...v1.8.0</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>minor de features: notas 3 New + 5 Improved vs 3 Fixed; 19/34 fixes mas correcao nao lidera</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -6723,6 +9147,16 @@
           <t>https://github.com/Fission-AI/OpenSpec/compare/v1.9.0...v1.10.0</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>secao Fixed com 8 itens lidera as notas; 10 de 18 commits sao correcoes contra apenas 2 feats</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -6756,6 +9190,16 @@
           <t>https://github.com/Fission-AI/OpenSpec/compare/v1.10.0...v1.11.0</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>destaque para 2 comandos novos (show --diff, status --all); notas 2 fixes vs 5 melhorias</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -6789,6 +9233,16 @@
           <t>https://github.com/mastodon/mastodon/compare/v4.4.7...v4.4.8</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>release so de seguranca: GHSA quote control bypass; 2 commits (merge de fork + bump)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -6822,6 +9276,16 @@
           <t>https://github.com/mastodon/mastodon/compare/v4.4.9...v4.5.2</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>notas apenas Changed(1) e Fixed(12); patch de bugs; commits de 840 refletem ramos inteiros</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -6855,6 +9319,16 @@
           <t>https://github.com/mastodon/mastodon/compare/v4.4.11...v4.3.17</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>security GHSA (SSRF e ownership check) + 1 fix; notas de correcao dominam patch 4.3</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -6888,6 +9362,16 @@
           <t>https://github.com/mastodon/mastodon/compare/v4.5.8...v4.4.15</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Security 2 + Fixed 8 vs Added 1 + Changed 2; patch 4.4 liderado por correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -6921,6 +9405,16 @@
           <t>https://github.com/mastodon/mastodon/compare/v4.6.3...v4.6.4</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Security 3 + Fixed 23 vs Changed 1; 23 dos 35 commits sao correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -6954,6 +9448,16 @@
           <t>https://github.com/Mintplex-Labs/anything-llm/compare/v1.8.5...v1.9.0</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>release de features: overhaul de @agent com streaming; 6 fixes em 63 itens de notas</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -6987,6 +9491,16 @@
           <t>https://github.com/Mintplex-Labs/anything-llm/compare/v1.9.0...v1.9.1</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Notable Changes sao features (PWA, providers, conector); 11 fixes em 62 itens de notas</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -7020,6 +9534,16 @@
           <t>https://github.com/Mintplex-Labs/anything-llm/compare/v1.11.1...v1.11.2</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>notas sao melhorias de UI e features; apenas 4 de 31 itens sao fixes</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -7053,6 +9577,16 @@
           <t>https://github.com/Mintplex-Labs/anything-llm/compare/v1.14.1...v1.14.2</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>patch misturado: 5 fixes e 5 feats em 15 commits; busca Brave e fastCRW entre correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -7086,6 +9620,16 @@
           <t>https://github.com/Mintplex-Labs/anything-llm/compare/v1.16.1...v1.16.2</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>secoes New Features (8) e Improvements (16) sem secao de fixes; notas orientadas a funcionalidade</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -7119,6 +9663,16 @@
           <t>https://github.com/Imbad0202/academic-research-skills/compare/v3.9.4.2...v3.10.0</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>minor de features (policy layer, eval harness, write guard); 19 feats vs 16 fixes</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -7152,6 +9706,16 @@
           <t>https://github.com/Imbad0202/academic-research-skills/compare/v3.10.0...v3.11.0</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>feature principal e o citation-existence gate #182; 5 feats vs 2 fixes em 14 commits</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -7185,6 +9749,16 @@
           <t>https://github.com/Imbad0202/academic-research-skills/compare/v3.17.0...v3.18.0</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>9 dos 10 commits sao feats; release de novos mecanismos de um survey</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -7218,6 +9792,16 @@
           <t>https://github.com/Imbad0202/academic-research-skills/compare/v3.19.0...v3.20.0</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>hardening/features: 21 feats e 21 chores vs 18 fixes; highlights de novos substratos</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -7251,6 +9835,16 @@
           <t>https://github.com/Imbad0202/academic-research-skills/compare/v3.20.0...v3.20.1</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>patch com 5 feats vs 1 fix; bundles claim-standing e assignment-ledger novos</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -7284,6 +9878,16 @@
           <t>https://github.com/pingcap/tidb/compare/v7.5.7...v8.5.4</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>release de patch TiDB; amostra 21 fixes vs 8 features em 62 de 3570 commits</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -7317,6 +9921,16 @@
           <t>https://github.com/pingcap/tidb/compare/v8.5.4...v8.5.5</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>patch TiDB; amostra 19 fixes vs 8 features; inclui fix de seguranca em x/oauth2</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -7350,6 +9964,16 @@
           <t>https://github.com/pingcap/tidb/compare/v8.5.5...v8.5.6</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>release notes oficiais do TiDB: 31 bug fixes vs 7 features e 8 melhorias</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -7383,6 +10007,16 @@
           <t>https://github.com/pingcap/tidb/compare/v8.5.7...v8.5.8</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>39 commits majoritariamente fixes, incluindo 2 DoS e deps vulneraveis; patch 8.5</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -7416,6 +10050,16 @@
           <t>https://github.com/pingcap/tidb/compare/v8.5.8...v7.5.8</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>patch 7.5; amostra 27 fixes vs 7 features em 62 de 849 commits</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -7449,6 +10093,16 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b8600...b8601</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>unico commit corrige parsing de tool calls gpt-oss; PR 21213 remove erros em evals</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -7482,6 +10136,16 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b9748...b9750</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>commits sao implement call statement e add load progress callback; funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -7515,6 +10179,16 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b9789...b9802</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>mistura de 6 fixes, 2 feats e 5 chores em 13 commits; release diaria rotineira</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -7548,6 +10222,16 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b9935...b9936</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>unico commit; PR 25420 declara fixes 25213 e 25320, regressao de velocidade de prefill</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -7581,6 +10265,16 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b10258...b10259</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>unico commit 'allow reshape of tensors during load' e funcionalidade, nao correcao</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -7614,6 +10308,16 @@
           <t>https://github.com/ChrisTitusTech/winutil/compare/25.09.05...25.10.06</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>mistura de novidades (System Restore, toggle offline, 25H2) e fixes; 7/17 commits fixes</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -7647,6 +10351,16 @@
           <t>https://github.com/ChrisTitusTech/winutil/compare/26.02.11...26.02.18</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>mistura: 4 features, 13 bug fixes e ~18 chores/docs; commits dominados por workflows</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -7680,6 +10394,16 @@
           <t>https://github.com/ChrisTitusTech/winutil/compare/26.02.18...26.03.03</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>6 features e 10 fixes + 14 docs; commits dominados por chores e documentacao</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -7713,6 +10437,16 @@
           <t>https://github.com/ChrisTitusTech/winutil/compare/26.04.21...26.04.30</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>mistura equilibrada 3 features e 3 fixes com 6 docs; rotina mensal</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -7746,6 +10480,16 @@
           <t>https://github.com/ChrisTitusTech/winutil/compare/26.05.12...26.06.23</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>release de limpeza e refatoracao; 1 fix de seguranca entre 137 commits de manutencao</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -7779,6 +10523,16 @@
           <t>https://github.com/crewAIInc/crewAI/compare/0.201.1...0.203.0</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>notas dominadas por documentacao e infra; apenas 2 fixes pequenos e 1 feat</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -7812,6 +10566,16 @@
           <t>https://github.com/crewAIInc/crewAI/compare/1.2.0...1.2.1</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>apenas 2 features e 2 docs; nenhuma correcao</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -7845,6 +10609,16 @@
           <t>https://github.com/crewAIInc/crewAI/compare/1.15.11...1.15.12</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>5 features vs 1 bug fix; release de funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -7878,6 +10652,16 @@
           <t>https://github.com/crewAIInc/crewAI/compare/1.15.17...1.15.18</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>quase equilibrio: 11 fixes vs 9 features; commits 12 fix vs 10 feat; mistura</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -7911,6 +10695,16 @@
           <t>https://github.com/crewAIInc/crewAI/compare/1.15.18...1.15.19</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>8 fixes vs 5 features, mas mistura com 6 feats e 7 chores; inclui bumps de dependencia</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -7944,6 +10738,16 @@
           <t>https://github.com/ToolJet/ToolJet/compare/v3.20.28-lts...v3.20.29-lts</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>features (OIDC PKCE, metricas, storybook) dominam; 13 feats vs 6 fixes em 51 commits</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -7977,6 +10781,16 @@
           <t>https://github.com/ToolJet/ToolJet/compare/v3.20.168-lts...v3.20.169-lts</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>release minuscula: 1 fix e 1 enhancement empatados e 4 chores de bump; rotina LTS</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -8010,6 +10824,16 @@
           <t>https://github.com/ToolJet/ToolJet/compare/v3.20.172-lts...v3.20.173-lts</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>2 features e 1 enhancement vs 1 fix; mistura com funcionalidades em destaque</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -8043,6 +10867,16 @@
           <t>https://github.com/ToolJet/ToolJet/compare/v3.20.187-lts...v3.20.188-lts</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>notas e commits somente correcoes (3 fixes de widgets) e 1 chore de submodules</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -8076,6 +10910,16 @@
           <t>https://github.com/ToolJet/ToolJet/compare/v3.20.230-lts...v3.20.231-lts</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Custom Component Library e Navigation dominam; 19 feats vs 4 fixes na amostra</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -8109,6 +10953,16 @@
           <t>https://github.com/browser-use/browser-use/compare/0.10.0...0.10.1</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>apenas bump de versao por pyproject esquecido; atualizacao de rotina</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -8142,6 +10996,16 @@
           <t>https://github.com/browser-use/browser-use/compare/0.11.2...0.11.3</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>mistura equilibrada de ~11 fixes e ~12 features/docs; release menor rotineira</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -8175,6 +11039,16 @@
           <t>https://github.com/browser-use/browser-use/compare/0.12.0...0.12.1</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>notas quase todas 'fix:' e 30 de 60 commits sao correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -8208,6 +11082,16 @@
           <t>https://github.com/browser-use/browser-use/compare/0.12.9...0.13.0</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>lanca novo agent beta em Rust; 250 commits de funcionalidade</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -8241,6 +11125,16 @@
           <t>https://github.com/browser-use/browser-use/compare/0.13.5...0.13.6</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>release so de versionamento do Browser Harness; apenas bump</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -8274,6 +11168,16 @@
           <t>https://github.com/danielmiessler/Fabric/compare/v1.4.338...v1.4.339</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Release traz apenas feat de anexos de imagem para Ollama; 4 commits de feature/chore</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -8307,6 +11211,16 @@
           <t>https://github.com/danielmiessler/Fabric/compare/v1.4.362...v1.4.363</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Refactor de qualidade de codigo (reuso de HTTP client); nenhum defeito corrigido</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -8340,6 +11254,16 @@
           <t>https://github.com/danielmiessler/Fabric/compare/v1.4.431...v1.4.432</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Chore de atualizacao de dependencias web; fix mencionado e do proprio npm override</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -8373,6 +11297,16 @@
           <t>https://github.com/danielmiessler/Fabric/compare/v1.4.468...v1.4.469</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Troca pipeline PDF.js por worker WASM (feat); 2 fixes incidentais entre 7 commits</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -8406,6 +11340,16 @@
           <t>https://github.com/danielmiessler/Fabric/compare/v1.4.476...v1.4.477</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Patch: unico commit efetivo e fix de vazamento de diretorio temporario + testes</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -8439,6 +11383,16 @@
           <t>https://github.com/career-ops-hq/career-ops/compare/career-ops-v1.14.0...career-ops-v1.15.0</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Notes iniciam em Features e ~25 dos 39 commits sao feats de providers/dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -8472,6 +11426,16 @@
           <t>https://github.com/career-ops-hq/career-ops/compare/web-v0.2.0...career-ops-v1.18.0</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Notes e commits dominados por features (i18n, providers, modos); fixes em minoria</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -8505,6 +11469,16 @@
           <t>https://github.com/career-ops-hq/career-ops/compare/career-ops-v1.33.0...web-v0.11.0</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Notes: 11 Bug Fixes contra 1 Feature; commits indisponiveis, corpo domina em fixes</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -8538,6 +11512,16 @@
           <t>https://github.com/career-ops-hq/career-ops/compare/web-v0.11.0...career-ops-v1.34.0</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>2 dos 4 highlights corrigem defeitos (update prompt e ofertas fechadas); 58% dos commits visiveis sao fixes</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -8571,6 +11555,16 @@
           <t>https://github.com/career-ops-hq/career-ops/compare/web-v0.12.0...career-ops-v1.35.0</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Objetivo declarado e feature: nine new job sources; highlights maioria funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -8604,6 +11598,16 @@
           <t>https://github.com/vercel-labs/agent-browser/compare/v0.7.4...v0.7.5</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Patch com unico changelog item corrigindo workflow de release do GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -8637,6 +11641,16 @@
           <t>https://github.com/vercel-labs/agent-browser/compare/v0.8.3...v0.8.4</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Release de patch: fix do erro Daemon not found resolvendo symlinks no PATH</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -8670,6 +11684,16 @@
           <t>https://github.com/vercel-labs/agent-browser/compare/agent-browser@0.23.0...v0.23.0</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>4 itens de fix contra 1 feat (dashboard); correcoes dominam a lista de changes</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -8703,6 +11727,16 @@
           <t>https://github.com/vercel-labs/agent-browser/compare/v0.25.4...v0.25.5</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Secao Bug Fixes exclusiva; 6 de 7 commits sao fixes de CDP, viewport e testes</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -8736,6 +11770,16 @@
           <t>https://github.com/vercel-labs/agent-browser/compare/v0.27.3...v0.28.0</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>New Features: MCP server e plugin system; nenhum item corretivo</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -8769,6 +11813,16 @@
           <t>https://github.com/ant-design/ant-design/compare/6.3.4...6.3.5</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Release de patch com 3 fixes no corpo; commits incluem chores de rotina</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -8802,6 +11856,16 @@
           <t>https://github.com/ant-design/ant-design/compare/6.3.5...6.3.6</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Notes de patch listam ~13 fixes e 2 perfs; correcoes dominam o changelog</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -8835,6 +11899,16 @@
           <t>https://github.com/ant-design/ant-design/compare/6.5.0...6.5.1</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Notes inteiras sao fixes de componentes; commits misturados com chores/docs</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -8868,6 +11942,16 @@
           <t>https://github.com/ant-design/ant-design/compare/6.5.2...6.5.3</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Corpo do patch lista apenas fixes (Input, DatePicker, Form) + 2 perfs</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -8901,6 +11985,16 @@
           <t>https://github.com/ant-design/ant-design/compare/6.5.3...6.5.4</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Corpo do patch lista somente fixes; 15 de 27 commits tambem sao fixes</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -8934,6 +12028,16 @@
           <t>https://github.com/ccxt/ccxt/compare/v4.5.7...v4.5.8</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Mistura semanal: 13 fixes contra 8 feats em 24 itens; correcoes em leve maioria</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -8967,6 +12071,16 @@
           <t>https://github.com/ccxt/ccxt/compare/v4.5.25...v4.5.26</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Release com unico PR de correcao de error handling do bitmart</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -9000,6 +12114,16 @@
           <t>https://github.com/ccxt/ccxt/compare/v4.5.29...v4.5.30</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>9 fixes contra 3 feats em 17 itens; correcoes em clara maioria</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -9033,6 +12157,16 @@
           <t>https://github.com/ccxt/ccxt/compare/v4.5.37...v4.5.38</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>12 fixes de mapeamento e parsing contra 1 feat de endpoints novos</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -9066,6 +12200,16 @@
           <t>https://github.com/ccxt/ccxt/compare/v4.5.38...v4.5.39</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Mistura equilibrada com leve maioria de feats (novos endpoints) sobre fixes</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -9099,6 +12243,16 @@
           <t>https://github.com/apple/container/compare/0.4.1...0.5.0</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Minor com breaking changes e features de CLI/API; apenas 2 correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -9132,6 +12286,16 @@
           <t>https://github.com/apple/container/compare/0.5.0...0.6.0</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Highlights de features (subnet, volumes, network none) superam as correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -9165,6 +12329,16 @@
           <t>https://github.com/apple/container/compare/0.11.0...0.12.0</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Largamente feature-driven (progresso, YAML, cap-add); fixes de build minoria</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -9198,6 +12372,16 @@
           <t>https://github.com/apple/container/compare/1.2.1...1.2.2</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Objetivo declarado no corpo: corrigir glitch do container k8s na instalacao</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -9231,6 +12415,16 @@
           <t>https://github.com/apple/container/compare/1.3.0...1.3.1</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Patch de seguranca corrigindo 6 advisories GHSA/CVE do Containerization</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -9264,6 +12458,16 @@
           <t>https://github.com/reactive-resume/reactive-resume/compare/v5.1.2...v5.1.3</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>18 de 42 commits sao fixes de PDF/CJK/schema; template novo e unico destaque feat</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -9297,6 +12501,16 @@
           <t>https://github.com/reactive-resume/reactive-resume/compare/v5.1.3...v5.1.4</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Destaque principal e o novo workspace de AI Agent; correcoes sao incidentais</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -9330,6 +12544,16 @@
           <t>https://github.com/reactive-resume/reactive-resume/compare/v5.2.2...v5.2.3</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Notes dominadas por features de provedores AI e exports; apenas 1 fix</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -9363,6 +12587,16 @@
           <t>https://github.com/reactive-resume/reactive-resume/compare/v5.2.4...v5.2.5</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Corpo mistura 1 fix e 1 feat; commits dominados por docs/SEO (14 de 29)</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -9396,6 +12630,16 @@
           <t>https://github.com/reactive-resume/reactive-resume/compare/v5.2.5...v5.2.6</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Corpo detalha ~12 fixes de PDF/auth vs 4 features; 15 de 39 commits sao fixes</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -9429,6 +12673,16 @@
           <t>https://github.com/rails/rails/compare/v8.0.3...v8.1.0</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Release maior com features e remocoes de deprecacoes do Rails 8.1</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -9462,6 +12716,16 @@
           <t>https://github.com/rails/rails/compare/v8.1.0...v7.0.9</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Patch de backport cujo corpo lista somente fixes e adicoes de gems</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -9495,6 +12759,16 @@
           <t>https://github.com/rails/rails/compare/v7.0.10...v7.1.6</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Corpo lista apenas correcoes de conexao/compat e secoes No changes</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -9528,6 +12802,16 @@
           <t>https://github.com/rails/rails/compare/v7.2.3...v8.0.4</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Patch com fixes de SQLite e composite PK; apenas 2 itens nao-corretivos</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -9561,6 +12845,16 @@
           <t>https://github.com/rails/rails/compare/v8.1.2...v7.2.3.1</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Patch de seguranca apenas com correcoes de CVEs em NumberConverter e DiskService</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -9594,6 +12888,16 @@
           <t>https://github.com/fastapi/fastapi/compare/0.118.0...0.118.1</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Rotina: upgrades, docs, traducoes e bumps de dependencias; sem correcao principal</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -9627,6 +12931,16 @@
           <t>https://github.com/fastapi/fastapi/compare/0.123.5...0.123.6</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Secao Fixes exclusiva com um unico bug de functools wraps e partial</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -9660,6 +12974,16 @@
           <t>https://github.com/fastapi/fastapi/compare/0.128.3...0.128.4</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Refactors internos, traducoes e upgrades de dev deps; nenhum defeito corrigido</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -9693,6 +13017,16 @@
           <t>https://github.com/fastapi/fastapi/compare/0.134.0...0.135.0</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Release de feature: suporte a Server Sent Events</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -9726,6 +13060,16 @@
           <t>https://github.com/fastapi/fastapi/compare/0.139.1...0.139.2</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Corpo exclusivo da secao Fixes: torna construcao de rotas thread-safe</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -9759,6 +13103,16 @@
           <t>https://github.com/react-hook-form/react-hook-form/compare/v7.70.0...v7.71.0</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>2 perfs e 1 chore superam o unico fix; correcao e minoritaria</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -9792,6 +13146,16 @@
           <t>https://github.com/react-hook-form/react-hook-form/compare/v7.74.0...v7.75.0</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>4 fixes contra 1 feat e 1 upgrade; correcoes sao a maioria dos itens</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -9825,6 +13189,16 @@
           <t>https://github.com/react-hook-form/react-hook-form/compare/v7.76.0...v7.76.1</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Patch corrige regressoes de setValues (2 fixes + reverts) apos 7.76.0</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -9858,6 +13232,16 @@
           <t>https://github.com/react-hook-form/react-hook-form/compare/v7.81.0...v7.82.0</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>5 fixes de dirtyFields/watch contra 1 feat delayError e 1 perf</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -9891,6 +13275,16 @@
           <t>https://github.com/react-hook-form/react-hook-form/compare/v7.85.0...v7.86.0</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>9 fixes contra 1 feat e 4 perfs; correcoes clara maioria do changelog</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -9924,6 +13318,16 @@
           <t>https://github.com/moeru-ai/airi/compare/v0.8.1-beta.4...v0.8.1-beta.11</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>notes 6 features vs 9 fixes e commits 18 fixes vs 11 feats em 60; beta misturada</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -9957,6 +13361,16 @@
           <t>https://github.com/moeru-ai/airi/compare/v0.8.1...v0.8.2</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>notes 13 fixes vs 9 features; commits 8 fixes vs 6 feats e 14 chores de rotina</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -9990,6 +13404,16 @@
           <t>https://github.com/moeru-ai/airi/compare/v0.9.0-alpha.24...v0.9.0-alpha.28</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>notes apenas secao Bug Fixes (3 itens); commits 3 fixes e nenhuma feature</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -10023,6 +13447,16 @@
           <t>https://github.com/moeru-ai/airi/compare/v0.9.0-beta.2...v0.9.0</t>
         </is>
       </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>milestone 0.9.0; commits 16 fixes vs 13 feats (55%) e notes misturadas com 48 feats</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -10056,6 +13490,16 @@
           <t>https://github.com/moeru-ai/airi/compare/v0.11.3...v0.12.0-beta.5</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>beta com features de destaque (MAGIC, VOICEVOX); notes ~6 fixes vs 5 features; commits 20 vs 12</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -10089,6 +13533,16 @@
           <t>https://github.com/janhq/jan/compare/v0.6.10...v0.7.0</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>milestone 0.7.0 (model selector, MCP, auth); fixes sao em sua maioria limpeza de branches feat</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -10122,6 +13576,16 @@
           <t>https://github.com/janhq/jan/compare/v0.7.4...v0.7.5</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>notes e commits apenas correcoes: 4 fixes (import Windows, CUDA, mcp) em 5 commits</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -10155,6 +13619,16 @@
           <t>https://github.com/janhq/jan/compare/v0.7.8...v0.7.9</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>patch 0.7.9; notes 18 fixes vs 10 feats e commits 11 de 13 alteracoes de codigo sao fixes</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -10188,6 +13662,16 @@
           <t>https://github.com/janhq/jan/compare/v0.8.0...v0.8.1</t>
         </is>
       </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>patch 0.8.1; notes 7 fixes nenhuma feature; commits 34 fixes vs 7 feats em 60</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -10221,6 +13705,16 @@
           <t>https://github.com/janhq/jan/compare/v0.8.2...v0.8.3</t>
         </is>
       </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>notes apenas correcoes (6 fixes, 0 feats); commits 25 fixes vs 17 feats; patch 0.8.3</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -10254,6 +13748,16 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.2.0...v0.2.1</t>
         </is>
       </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>sem commits; notes citam pnpm e Vitest (features) e fix de argumentos e secundario</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -10287,6 +13791,16 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.8.1...v0.9.0</t>
         </is>
       </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>notes 7 features vs 3 fixes e commits 6 feats vs 5 fixes; release de funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -10320,6 +13834,16 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.13.1...v0.14.0</t>
         </is>
       </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>so 4 commits; 2 'fixes' sao URLs/metadata de rotina e 1 feat de CI (Homebrew)</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -10353,6 +13877,16 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.40.0...v0.41.0</t>
         </is>
       </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>notes 17 fixes vs 1 feature; commits 15 fixes vs 1 feat em 42 (inclui path traversal)</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -10386,6 +13920,16 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.44.2...v0.45.0</t>
         </is>
       </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>commits 11 fixes vs 2 feats (85%); notes 3 fixes vs 2 features de hooks/rewrite</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -10419,6 +13963,16 @@
           <t>https://github.com/calcom/cal.diy/compare/v5.7.7...v5.7.8</t>
         </is>
       </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>mistura equilibrada: notes 14 fixes vs 9 feats e commits 14 vs 10, traz features PBAC/UI</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -10452,6 +14006,16 @@
           <t>https://github.com/calcom/cal.diy/compare/v5.7.11...v5.7.12</t>
         </is>
       </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>8 feats (PBAC, spam blocker, workflows) vs 9 fixes; mistura sem dominio de correcao</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -10485,6 +14049,16 @@
           <t>https://github.com/calcom/cal.diy/compare/v5.8.14...v5.9.0</t>
         </is>
       </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>unico conteudo das notes e dos commits e uma correcao (timezone badge); 1 fix + release</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -10518,6 +14092,16 @@
           <t>https://github.com/calcom/cal.diy/compare/v6.0.10...v6.0.11</t>
         </is>
       </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>notes 16 feats vs 15 fixes e commits 16 vs 15; mistura equilibrada com funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -10551,6 +14135,16 @@
           <t>https://github.com/calcom/cal.diy/compare/v6.1.1...v6.1.2</t>
         </is>
       </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>commits 11 feats vs 11 fixes e notes 11 vs 13; mistura equilibrada com funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -10584,6 +14178,16 @@
           <t>https://github.com/zed-industries/zed/compare/v0.212.7...v0.213.3</t>
         </is>
       </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>release semanal; secoes Features ~46 vs Bug Fixes 51 e intro destaca Gemini 3 Pro</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -10617,6 +14221,16 @@
           <t>https://github.com/zed-industries/zed/compare/v0.217.1...v0.217.2</t>
         </is>
       </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>notes e commits apenas funcionalidades (Gemini 3 Flash, ty); zero correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -10650,6 +14264,16 @@
           <t>https://github.com/zed-industries/zed/compare/v0.220.2...v0.220.3</t>
         </is>
       </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>release inteira e a correcao de regressao de permissao de tool calls; 2 commits</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -10683,6 +14307,16 @@
           <t>https://github.com/zed-industries/zed/compare/v0.224.6...v0.224.7</t>
         </is>
       </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>2 fixes (panic, colorizacao) vs 1 feature (Gemini 3.1 Pro) em 3 commits de codigo</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -10716,6 +14350,16 @@
           <t>https://github.com/zed-industries/zed/compare/v1.13.1...v1.13.2</t>
         </is>
       </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>3 fixes e 1 doc; notes e commits sem funcionalidades novas no patch 1.13.2</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -10749,6 +14393,16 @@
           <t>https://github.com/typst/typst/compare/v0.13.1...v0.14.0</t>
         </is>
       </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>release 0.14.0 de funcionalidades (PDF acessivel, PDF/A, HTML); Highlights sao features</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -10782,6 +14436,16 @@
           <t>https://github.com/typst/typst/compare/v0.14.0...v0.14.1</t>
         </is>
       </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>notes cheias de Fixed (22) sem features; commits 15 fixes e 0 feats em 48</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -10815,6 +14479,16 @@
           <t>https://github.com/typst/typst/compare/v0.14.1...v0.14.2</t>
         </is>
       </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>release de seguranca: vulnerabilidade use-after-free no wasmi; bump + correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -10848,6 +14522,16 @@
           <t>https://github.com/typst/typst/compare/v0.14.2...v0.15.0</t>
         </is>
       </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>release 0.15.0 com 14 Highlights de features (fontes variaveis, MathML, bundle)</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -10881,6 +14565,16 @@
           <t>https://github.com/typst/typst/compare/v0.15.0...v0.15.1</t>
         </is>
       </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>notes apenas correcoes de regressoes (math, layout, SVG); commits 6 fixes e 0 feats</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -10914,6 +14608,16 @@
           <t>https://github.com/denoland/deno/compare/v2.7.7...v2.7.8</t>
         </is>
       </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>notes 50 fixes vs 6 features; commits 39 fixes vs 6 feats em 60</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -10947,6 +14651,16 @@
           <t>https://github.com/denoland/deno/compare/v2.7.8...v2.7.9</t>
         </is>
       </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>notes e commits apenas correcoes (10 fixes, 0 features) no patch 2.7.9</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -10980,6 +14694,16 @@
           <t>https://github.com/denoland/deno/compare/v2.8.2...v2.8.3</t>
         </is>
       </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>notes 170 fixes vs 26 feats; commits 38 fixes vs 9 feats em 60 (87%)</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -11013,6 +14737,16 @@
           <t>https://github.com/denoland/deno/compare/v2.9.0...v2.9.1</t>
         </is>
       </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>notes 41 fixes vs 3 features; commits 41 fixes vs 3 feats em 54 (93%)</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -11046,6 +14780,16 @@
           <t>https://github.com/denoland/deno/compare/v2.9.1...v2.9.2</t>
         </is>
       </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>notes 54 fixes vs 10 feats; commits 33 fixes vs 5 feats em 60 (87%)</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -11079,6 +14823,16 @@
           <t>https://github.com/dani-garcia/vaultwarden/compare/1.34.3...1.35.0</t>
         </is>
       </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>destaque de 1.35.0 sao features (SSO OpenID, web vault novo) apesar de 24 fixes</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -11112,6 +14866,16 @@
           <t>https://github.com/dani-garcia/vaultwarden/compare/1.35.4...1.35.5</t>
         </is>
       </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>secao Security Fixes com 3 advisories; release para corrigir falhas de seguranca</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -11145,6 +14909,16 @@
           <t>https://github.com/dani-garcia/vaultwarden/compare/1.35.8...1.36.0</t>
         </is>
       </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>secao Security Fixes com 5 advisories (CSRF, enumeracao, SSRF) dominam a release</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -11178,6 +14952,16 @@
           <t>https://github.com/dani-garcia/vaultwarden/compare/1.37.0...1.37.1</t>
         </is>
       </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>patch so para corrigir invites e build Alpine; 1 commit de correcao, 0 funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -11211,6 +14995,16 @@
           <t>https://github.com/dani-garcia/vaultwarden/compare/1.37.1...1.37.2</t>
         </is>
       </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>5 de 6 itens sao correcoes; release de manutencao p/ compatibilidade clientes 2026.8+</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -11244,6 +15038,16 @@
           <t>https://github.com/nexu-io/open-design/compare/open-design-v0.4.1...open-design-v0.5.0</t>
         </is>
       </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>0.5.0 destaca dashboards, Inspect mode e tema (features); 13 feats vs 23 fixes nos commits</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -11277,6 +15081,16 @@
           <t>https://github.com/nexu-io/open-design/compare/open-design-v0.12.0...open-design-v0.13.0</t>
         </is>
       </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>notes destacam resume de sessao e BYOK (features); commits 16 fixes vs 15 feats - equilibrado</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -11310,6 +15124,16 @@
           <t>https://github.com/nexu-io/open-design/compare/open-design-v0.15.0...open-design-v0.15.1</t>
         </is>
       </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>secao Fixed com 12 itens vs 3 Added; commits 42 fixes vs 10 feats (81%)</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -11343,6 +15167,16 @@
           <t>https://github.com/nexu-io/open-design/compare/open-design-v0.20.2...open-design-v0.21.0</t>
         </is>
       </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>destaques sao confiabilidade; secao Fixed 18 itens vs 3 Added; commits 31 fixes vs 10 feats</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -11376,6 +15210,16 @@
           <t>https://github.com/nexu-io/open-design/compare/open-design-v0.23.0...open-design-v0.24.0</t>
         </is>
       </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>secao Fixed 11 itens vs 1 Added; commits 37 fixes vs 4 feats (90%)</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -11409,6 +15253,16 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.11.7...v1.12.0</t>
         </is>
       </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>release menor 1.12.0 (milestone) que aponta NEWS.md; release de funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -11442,6 +15296,16 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.12.3...v1.12.4</t>
         </is>
       </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>patch de backports apenas com fixes (overflow, JET, docs) e 0 funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -11475,6 +15339,16 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.10.11...v1.12.6</t>
         </is>
       </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>patch 1.12.6 so com correcoes/backports; commits 10 fixes e 0 feats na amostra</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -11508,6 +15382,16 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.12.7...v1.10.12</t>
         </is>
       </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>patch LTS 1.10.12 so com correcoes; commits 11 fixes e 0 feats na amostra</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -11539,6 +15423,16 @@
       <c r="G301" s="2" t="inlineStr">
         <is>
           <t>https://github.com/JuliaLang/julia/compare/v1.10.12...v1.13.0</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>release menor 1.13.0 (milestone) com novas funcionalidades; notes apontam NEWS.md</t>
         </is>
       </c>
     </row>
